--- a/artfynd/A 40735-2024 artfynd.xlsx
+++ b/artfynd/A 40735-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121072525</v>
+        <v>121072523</v>
       </c>
       <c r="B6" t="n">
-        <v>57459</v>
+        <v>79708</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,38 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545931</v>
+        <v>545932</v>
       </c>
       <c r="R6" t="n">
-        <v>7206731</v>
+        <v>7206629</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121072523</v>
+        <v>121072525</v>
       </c>
       <c r="B7" t="n">
-        <v>79708</v>
+        <v>57459</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,34 +1251,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545932</v>
+        <v>545931</v>
       </c>
       <c r="R7" t="n">
-        <v>7206629</v>
+        <v>7206731</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2596,10 +2596,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121072532</v>
+        <v>121072543</v>
       </c>
       <c r="B19" t="n">
-        <v>90687</v>
+        <v>78598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545926</v>
+        <v>545935</v>
       </c>
       <c r="R19" t="n">
-        <v>7206732</v>
+        <v>7206821</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121072543</v>
+        <v>121072532</v>
       </c>
       <c r="B20" t="n">
-        <v>78598</v>
+        <v>90687</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,21 +2724,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545935</v>
+        <v>545926</v>
       </c>
       <c r="R20" t="n">
-        <v>7206821</v>
+        <v>7206732</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 40735-2024 artfynd.xlsx
+++ b/artfynd/A 40735-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072546</v>
+        <v>121072541</v>
       </c>
       <c r="B2" t="n">
-        <v>94474</v>
+        <v>90983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545881</v>
+        <v>545935</v>
       </c>
       <c r="R2" t="n">
-        <v>7206905</v>
+        <v>7206821</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072534</v>
+        <v>121072521</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>97035</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545926</v>
+        <v>545947</v>
       </c>
       <c r="R3" t="n">
-        <v>7206745</v>
+        <v>7206549</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121072547</v>
+        <v>121072527</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>90662</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545876</v>
+        <v>545934</v>
       </c>
       <c r="R4" t="n">
-        <v>7206904</v>
+        <v>7206732</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121072522</v>
+        <v>121072539</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545943</v>
+        <v>545930</v>
       </c>
       <c r="R5" t="n">
-        <v>7206552</v>
+        <v>7206838</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
         <v>121072523</v>
       </c>
       <c r="B6" t="n">
-        <v>79708</v>
+        <v>79711</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121072525</v>
+        <v>121072547</v>
       </c>
       <c r="B7" t="n">
-        <v>57459</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,42 +1247,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545931</v>
+        <v>545876</v>
       </c>
       <c r="R7" t="n">
-        <v>7206731</v>
+        <v>7206904</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1350,7 @@
         <v>121072524</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1463,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072527</v>
+        <v>121072543</v>
       </c>
       <c r="B9" t="n">
-        <v>90652</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545934</v>
+        <v>545935</v>
       </c>
       <c r="R9" t="n">
-        <v>7206732</v>
+        <v>7206821</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1538,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121072545</v>
+        <v>121072533</v>
       </c>
       <c r="B10" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545915</v>
+        <v>545921</v>
       </c>
       <c r="R10" t="n">
-        <v>7206859</v>
+        <v>7206728</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121072536</v>
+        <v>121072530</v>
       </c>
       <c r="B11" t="n">
-        <v>57348</v>
+        <v>90983</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,43 +1699,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545912</v>
+        <v>545921</v>
       </c>
       <c r="R11" t="n">
-        <v>7206852</v>
+        <v>7206728</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1771,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072537</v>
+        <v>121072520</v>
       </c>
       <c r="B12" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545912</v>
+        <v>545961</v>
       </c>
       <c r="R12" t="n">
-        <v>7206852</v>
+        <v>7206539</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1883,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121072539</v>
+        <v>121072546</v>
       </c>
       <c r="B13" t="n">
-        <v>78598</v>
+        <v>94484</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1960,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545930</v>
+        <v>545881</v>
       </c>
       <c r="R13" t="n">
-        <v>7206838</v>
+        <v>7206905</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1995,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121072529</v>
+        <v>121072525</v>
       </c>
       <c r="B14" t="n">
-        <v>91127</v>
+        <v>57462</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,38 +2031,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545921</v>
+        <v>545931</v>
       </c>
       <c r="R14" t="n">
-        <v>7206726</v>
+        <v>7206731</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2107,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121072541</v>
+        <v>121072542</v>
       </c>
       <c r="B15" t="n">
-        <v>90973</v>
+        <v>90697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,21 +2151,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2256,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121072533</v>
+        <v>121072534</v>
       </c>
       <c r="B16" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545921</v>
+        <v>545926</v>
       </c>
       <c r="R16" t="n">
-        <v>7206728</v>
+        <v>7206745</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2331,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121072540</v>
+        <v>121072538</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>90711</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,21 +2375,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2408,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545926</v>
+        <v>545929</v>
       </c>
       <c r="R17" t="n">
-        <v>7206832</v>
+        <v>7206834</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2443,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121072548</v>
+        <v>121072531</v>
       </c>
       <c r="B18" t="n">
-        <v>57501</v>
+        <v>88024</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,38 +2487,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545861</v>
+        <v>545922</v>
       </c>
       <c r="R18" t="n">
-        <v>7206925</v>
+        <v>7206730</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2559,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2569,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2596,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121072543</v>
+        <v>121072519</v>
       </c>
       <c r="B19" t="n">
-        <v>78598</v>
+        <v>90693</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2612,21 +2599,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2636,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545935</v>
+        <v>545961</v>
       </c>
       <c r="R19" t="n">
-        <v>7206821</v>
+        <v>7206532</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2671,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2681,7 +2668,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121072532</v>
+        <v>121072537</v>
       </c>
       <c r="B20" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,21 +2711,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2748,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545926</v>
+        <v>545912</v>
       </c>
       <c r="R20" t="n">
-        <v>7206732</v>
+        <v>7206852</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2783,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2793,7 +2780,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2820,10 +2807,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121072530</v>
+        <v>121072548</v>
       </c>
       <c r="B21" t="n">
-        <v>90973</v>
+        <v>57504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2836,34 +2823,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545921</v>
+        <v>545861</v>
       </c>
       <c r="R21" t="n">
-        <v>7206728</v>
+        <v>7206925</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2895,7 +2886,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2905,7 +2896,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2932,10 +2923,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121072531</v>
+        <v>121072532</v>
       </c>
       <c r="B22" t="n">
-        <v>88018</v>
+        <v>90697</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2948,21 +2939,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2972,10 +2963,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545922</v>
+        <v>545926</v>
       </c>
       <c r="R22" t="n">
-        <v>7206730</v>
+        <v>7206732</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3044,10 +3035,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121072538</v>
+        <v>121072526</v>
       </c>
       <c r="B23" t="n">
-        <v>90701</v>
+        <v>94484</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3056,25 +3047,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3084,10 +3075,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545929</v>
+        <v>545931</v>
       </c>
       <c r="R23" t="n">
-        <v>7206834</v>
+        <v>7206732</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3119,7 +3110,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3129,7 +3120,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,10 +3147,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121072542</v>
+        <v>121072540</v>
       </c>
       <c r="B24" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3172,21 +3163,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3196,10 +3187,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545935</v>
+        <v>545926</v>
       </c>
       <c r="R24" t="n">
-        <v>7206821</v>
+        <v>7206832</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3231,7 +3222,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3241,7 +3232,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3271,7 +3262,7 @@
         <v>121072528</v>
       </c>
       <c r="B25" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3380,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121072544</v>
+        <v>121072522</v>
       </c>
       <c r="B26" t="n">
-        <v>79708</v>
+        <v>78601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3392,25 +3383,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3420,10 +3411,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545917</v>
+        <v>545943</v>
       </c>
       <c r="R26" t="n">
-        <v>7206851</v>
+        <v>7206552</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3455,7 +3446,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3465,7 +3456,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3492,10 +3483,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121072520</v>
+        <v>121072535</v>
       </c>
       <c r="B27" t="n">
-        <v>78598</v>
+        <v>94484</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3504,25 +3495,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3532,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545961</v>
+        <v>545913</v>
       </c>
       <c r="R27" t="n">
-        <v>7206539</v>
+        <v>7206851</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3567,7 +3558,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3577,7 +3568,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3604,10 +3595,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121072526</v>
+        <v>121072529</v>
       </c>
       <c r="B28" t="n">
-        <v>94474</v>
+        <v>91137</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3616,25 +3607,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3644,10 +3635,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545931</v>
+        <v>545921</v>
       </c>
       <c r="R28" t="n">
-        <v>7206732</v>
+        <v>7206726</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3679,7 +3670,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3689,7 +3680,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3716,10 +3707,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121072519</v>
+        <v>121072544</v>
       </c>
       <c r="B29" t="n">
-        <v>90683</v>
+        <v>79711</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3728,25 +3719,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3756,10 +3747,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545961</v>
+        <v>545917</v>
       </c>
       <c r="R29" t="n">
-        <v>7206532</v>
+        <v>7206851</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3791,7 +3782,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3801,7 +3792,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,7 +3822,7 @@
         <v>121072518</v>
       </c>
       <c r="B30" t="n">
-        <v>91042</v>
+        <v>91052</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3940,10 +3931,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121072535</v>
+        <v>121072545</v>
       </c>
       <c r="B31" t="n">
-        <v>94474</v>
+        <v>78601</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3952,25 +3943,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3980,10 +3971,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545913</v>
+        <v>545915</v>
       </c>
       <c r="R31" t="n">
-        <v>7206851</v>
+        <v>7206859</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4015,7 +4006,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4025,7 +4016,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4052,10 +4043,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121072521</v>
+        <v>121072536</v>
       </c>
       <c r="B32" t="n">
-        <v>97025</v>
+        <v>57351</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4064,38 +4055,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545947</v>
+        <v>545912</v>
       </c>
       <c r="R32" t="n">
-        <v>7206549</v>
+        <v>7206852</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 40735-2024 artfynd.xlsx
+++ b/artfynd/A 40735-2024 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072520</v>
+        <v>121072546</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>94484</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545961</v>
+        <v>545881</v>
       </c>
       <c r="R12" t="n">
-        <v>7206539</v>
+        <v>7206905</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121072546</v>
+        <v>121072520</v>
       </c>
       <c r="B13" t="n">
-        <v>94484</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545881</v>
+        <v>545961</v>
       </c>
       <c r="R13" t="n">
-        <v>7206905</v>
+        <v>7206539</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2807,10 +2807,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121072548</v>
+        <v>121072532</v>
       </c>
       <c r="B21" t="n">
-        <v>57504</v>
+        <v>90697</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2823,38 +2823,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545861</v>
+        <v>545926</v>
       </c>
       <c r="R21" t="n">
-        <v>7206925</v>
+        <v>7206732</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2886,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2896,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2923,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121072532</v>
+        <v>121072548</v>
       </c>
       <c r="B22" t="n">
-        <v>90697</v>
+        <v>57504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2939,34 +2935,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545926</v>
+        <v>545861</v>
       </c>
       <c r="R22" t="n">
-        <v>7206732</v>
+        <v>7206925</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3147,7 +3147,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121072540</v>
+        <v>121072522</v>
       </c>
       <c r="B24" t="n">
         <v>78601</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545926</v>
+        <v>545943</v>
       </c>
       <c r="R24" t="n">
-        <v>7206832</v>
+        <v>7206552</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,7 +3259,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121072528</v>
+        <v>121072540</v>
       </c>
       <c r="B25" t="n">
         <v>78601</v>
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545935</v>
+        <v>545926</v>
       </c>
       <c r="R25" t="n">
-        <v>7206733</v>
+        <v>7206832</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,7 +3371,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121072522</v>
+        <v>121072528</v>
       </c>
       <c r="B26" t="n">
         <v>78601</v>
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545943</v>
+        <v>545935</v>
       </c>
       <c r="R26" t="n">
-        <v>7206552</v>
+        <v>7206733</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3595,10 +3595,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121072529</v>
+        <v>121072544</v>
       </c>
       <c r="B28" t="n">
-        <v>91137</v>
+        <v>79711</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3607,25 +3607,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545921</v>
+        <v>545917</v>
       </c>
       <c r="R28" t="n">
-        <v>7206726</v>
+        <v>7206851</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3707,10 +3707,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121072544</v>
+        <v>121072529</v>
       </c>
       <c r="B29" t="n">
-        <v>79711</v>
+        <v>91137</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3719,25 +3719,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545917</v>
+        <v>545921</v>
       </c>
       <c r="R29" t="n">
-        <v>7206851</v>
+        <v>7206726</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 40735-2024 artfynd.xlsx
+++ b/artfynd/A 40735-2024 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072546</v>
+        <v>121072520</v>
       </c>
       <c r="B12" t="n">
-        <v>94484</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545881</v>
+        <v>545961</v>
       </c>
       <c r="R12" t="n">
-        <v>7206905</v>
+        <v>7206539</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121072520</v>
+        <v>121072546</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>94484</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545961</v>
+        <v>545881</v>
       </c>
       <c r="R13" t="n">
-        <v>7206539</v>
+        <v>7206905</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3147,7 +3147,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121072522</v>
+        <v>121072540</v>
       </c>
       <c r="B24" t="n">
         <v>78601</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545943</v>
+        <v>545926</v>
       </c>
       <c r="R24" t="n">
-        <v>7206552</v>
+        <v>7206832</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,7 +3259,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121072540</v>
+        <v>121072528</v>
       </c>
       <c r="B25" t="n">
         <v>78601</v>
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545926</v>
+        <v>545935</v>
       </c>
       <c r="R25" t="n">
-        <v>7206832</v>
+        <v>7206733</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,7 +3371,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121072528</v>
+        <v>121072522</v>
       </c>
       <c r="B26" t="n">
         <v>78601</v>
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545935</v>
+        <v>545943</v>
       </c>
       <c r="R26" t="n">
-        <v>7206733</v>
+        <v>7206552</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3595,10 +3595,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121072544</v>
+        <v>121072529</v>
       </c>
       <c r="B28" t="n">
-        <v>79711</v>
+        <v>91137</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3607,25 +3607,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545917</v>
+        <v>545921</v>
       </c>
       <c r="R28" t="n">
-        <v>7206851</v>
+        <v>7206726</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3707,10 +3707,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121072529</v>
+        <v>121072544</v>
       </c>
       <c r="B29" t="n">
-        <v>91137</v>
+        <v>79711</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3719,25 +3719,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545921</v>
+        <v>545917</v>
       </c>
       <c r="R29" t="n">
-        <v>7206726</v>
+        <v>7206851</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 40735-2024 artfynd.xlsx
+++ b/artfynd/A 40735-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072541</v>
+        <v>121072532</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545935</v>
+        <v>545926</v>
       </c>
       <c r="R2" t="n">
-        <v>7206821</v>
+        <v>7206732</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072521</v>
+        <v>121072539</v>
       </c>
       <c r="B3" t="n">
-        <v>97035</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545947</v>
+        <v>545930</v>
       </c>
       <c r="R3" t="n">
-        <v>7206549</v>
+        <v>7206838</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121072527</v>
+        <v>121072545</v>
       </c>
       <c r="B4" t="n">
-        <v>90662</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545934</v>
+        <v>545915</v>
       </c>
       <c r="R4" t="n">
-        <v>7206732</v>
+        <v>7206859</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121072539</v>
+        <v>121072525</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>57462</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1023,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545930</v>
+        <v>545931</v>
       </c>
       <c r="R5" t="n">
-        <v>7206838</v>
+        <v>7206731</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121072523</v>
+        <v>121072543</v>
       </c>
       <c r="B6" t="n">
-        <v>79711</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1139,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545932</v>
+        <v>545935</v>
       </c>
       <c r="R6" t="n">
-        <v>7206629</v>
+        <v>7206821</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121072547</v>
+        <v>121072546</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>94484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1251,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545876</v>
+        <v>545881</v>
       </c>
       <c r="R7" t="n">
-        <v>7206904</v>
+        <v>7206905</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121072524</v>
+        <v>121072530</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>90983</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545934</v>
+        <v>545921</v>
       </c>
       <c r="R8" t="n">
-        <v>7206628</v>
+        <v>7206728</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1463,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072543</v>
+        <v>121072534</v>
       </c>
       <c r="B9" t="n">
         <v>78601</v>
@@ -1499,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545935</v>
+        <v>545926</v>
       </c>
       <c r="R9" t="n">
-        <v>7206821</v>
+        <v>7206745</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121072533</v>
+        <v>121072536</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,34 +1591,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545921</v>
+        <v>545912</v>
       </c>
       <c r="R10" t="n">
-        <v>7206728</v>
+        <v>7206852</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121072530</v>
+        <v>121072523</v>
       </c>
       <c r="B11" t="n">
-        <v>90983</v>
+        <v>79711</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1708,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545921</v>
+        <v>545932</v>
       </c>
       <c r="R11" t="n">
-        <v>7206728</v>
+        <v>7206629</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1808,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072520</v>
+        <v>121072524</v>
       </c>
       <c r="B12" t="n">
         <v>78601</v>
@@ -1835,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545961</v>
+        <v>545934</v>
       </c>
       <c r="R12" t="n">
-        <v>7206539</v>
+        <v>7206628</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,7 +1920,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121072546</v>
+        <v>121072526</v>
       </c>
       <c r="B13" t="n">
         <v>94484</v>
@@ -1947,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545881</v>
+        <v>545931</v>
       </c>
       <c r="R13" t="n">
-        <v>7206905</v>
+        <v>7206732</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121072525</v>
+        <v>121072521</v>
       </c>
       <c r="B14" t="n">
-        <v>57462</v>
+        <v>97035</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,38 +2048,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545931</v>
+        <v>545947</v>
       </c>
       <c r="R14" t="n">
-        <v>7206731</v>
+        <v>7206549</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2098,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121072542</v>
+        <v>121072548</v>
       </c>
       <c r="B15" t="n">
-        <v>90697</v>
+        <v>57504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,34 +2160,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545935</v>
+        <v>545861</v>
       </c>
       <c r="R15" t="n">
-        <v>7206821</v>
+        <v>7206925</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2210,7 +2223,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2233,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121072534</v>
+        <v>121072531</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>88024</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,21 +2276,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2287,10 +2300,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545926</v>
+        <v>545922</v>
       </c>
       <c r="R16" t="n">
-        <v>7206745</v>
+        <v>7206730</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2322,7 +2335,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,7 +2345,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,10 +2372,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121072538</v>
+        <v>121072519</v>
       </c>
       <c r="B17" t="n">
-        <v>90711</v>
+        <v>90693</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2375,21 +2388,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2399,10 +2412,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545929</v>
+        <v>545961</v>
       </c>
       <c r="R17" t="n">
-        <v>7206834</v>
+        <v>7206532</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2434,7 +2447,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2457,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,10 +2484,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121072531</v>
+        <v>121072520</v>
       </c>
       <c r="B18" t="n">
-        <v>88024</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2487,21 +2500,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2511,10 +2524,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545922</v>
+        <v>545961</v>
       </c>
       <c r="R18" t="n">
-        <v>7206730</v>
+        <v>7206539</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2546,7 +2559,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2569,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2596,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121072519</v>
+        <v>121072542</v>
       </c>
       <c r="B19" t="n">
-        <v>90693</v>
+        <v>90697</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,21 +2612,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2636,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545961</v>
+        <v>545935</v>
       </c>
       <c r="R19" t="n">
-        <v>7206532</v>
+        <v>7206821</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2658,7 +2671,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2681,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,10 +2708,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121072537</v>
+        <v>121072527</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>90662</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,25 +2720,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2735,10 +2748,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545912</v>
+        <v>545934</v>
       </c>
       <c r="R20" t="n">
-        <v>7206852</v>
+        <v>7206732</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2770,7 +2783,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2793,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,10 +2820,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121072532</v>
+        <v>121072538</v>
       </c>
       <c r="B21" t="n">
-        <v>90697</v>
+        <v>90711</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2823,21 +2836,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2847,10 +2860,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545926</v>
+        <v>545929</v>
       </c>
       <c r="R21" t="n">
-        <v>7206732</v>
+        <v>7206834</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,7 +2895,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2905,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,10 +2932,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121072548</v>
+        <v>121072540</v>
       </c>
       <c r="B22" t="n">
-        <v>57504</v>
+        <v>78601</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2935,38 +2948,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545861</v>
+        <v>545926</v>
       </c>
       <c r="R22" t="n">
-        <v>7206925</v>
+        <v>7206832</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2998,7 +3007,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3008,7 +3017,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,10 +3044,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121072526</v>
+        <v>121072541</v>
       </c>
       <c r="B23" t="n">
-        <v>94484</v>
+        <v>90983</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3047,25 +3056,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3075,10 +3084,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545931</v>
+        <v>545935</v>
       </c>
       <c r="R23" t="n">
-        <v>7206732</v>
+        <v>7206821</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3110,7 +3119,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3120,7 +3129,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3147,10 +3156,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121072540</v>
+        <v>121072535</v>
       </c>
       <c r="B24" t="n">
-        <v>78601</v>
+        <v>94484</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3159,25 +3168,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3187,10 +3196,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545926</v>
+        <v>545913</v>
       </c>
       <c r="R24" t="n">
-        <v>7206832</v>
+        <v>7206851</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3222,7 +3231,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3232,7 +3241,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,7 +3268,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121072528</v>
+        <v>121072533</v>
       </c>
       <c r="B25" t="n">
         <v>78601</v>
@@ -3299,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545935</v>
+        <v>545921</v>
       </c>
       <c r="R25" t="n">
-        <v>7206733</v>
+        <v>7206728</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3334,7 +3343,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3344,7 +3353,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,7 +3380,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121072522</v>
+        <v>121072547</v>
       </c>
       <c r="B26" t="n">
         <v>78601</v>
@@ -3411,10 +3420,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545943</v>
+        <v>545876</v>
       </c>
       <c r="R26" t="n">
-        <v>7206552</v>
+        <v>7206904</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3446,7 +3455,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3456,7 +3465,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3483,10 +3492,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121072535</v>
+        <v>121072518</v>
       </c>
       <c r="B27" t="n">
-        <v>94484</v>
+        <v>91052</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3495,25 +3504,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2809</v>
+        <v>1506</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3523,10 +3532,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545913</v>
+        <v>545963</v>
       </c>
       <c r="R27" t="n">
-        <v>7206851</v>
+        <v>7206536</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3558,7 +3567,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3568,7 +3577,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3595,10 +3604,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121072529</v>
+        <v>121072544</v>
       </c>
       <c r="B28" t="n">
-        <v>91137</v>
+        <v>79711</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3607,25 +3616,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3635,10 +3644,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545921</v>
+        <v>545917</v>
       </c>
       <c r="R28" t="n">
-        <v>7206726</v>
+        <v>7206851</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3670,7 +3679,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3680,7 +3689,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3707,10 +3716,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121072544</v>
+        <v>121072529</v>
       </c>
       <c r="B29" t="n">
-        <v>79711</v>
+        <v>91137</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3719,25 +3728,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3747,10 +3756,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545917</v>
+        <v>545921</v>
       </c>
       <c r="R29" t="n">
-        <v>7206851</v>
+        <v>7206726</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3782,7 +3791,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3792,7 +3801,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3819,10 +3828,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121072518</v>
+        <v>121072537</v>
       </c>
       <c r="B30" t="n">
-        <v>91052</v>
+        <v>78601</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3831,25 +3840,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3859,10 +3868,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545963</v>
+        <v>545912</v>
       </c>
       <c r="R30" t="n">
-        <v>7206536</v>
+        <v>7206852</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3894,7 +3903,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3904,7 +3913,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3931,7 +3940,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121072545</v>
+        <v>121072528</v>
       </c>
       <c r="B31" t="n">
         <v>78601</v>
@@ -3971,10 +3980,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545915</v>
+        <v>545935</v>
       </c>
       <c r="R31" t="n">
-        <v>7206859</v>
+        <v>7206733</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4006,7 +4015,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4016,7 +4025,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4043,10 +4052,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121072536</v>
+        <v>121072522</v>
       </c>
       <c r="B32" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4059,43 +4068,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545912</v>
+        <v>545943</v>
       </c>
       <c r="R32" t="n">
-        <v>7206852</v>
+        <v>7206552</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 40735-2024 artfynd.xlsx
+++ b/artfynd/A 40735-2024 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121072525</v>
+        <v>121072543</v>
       </c>
       <c r="B5" t="n">
-        <v>57462</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,42 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545931</v>
+        <v>545935</v>
       </c>
       <c r="R5" t="n">
-        <v>7206731</v>
+        <v>7206821</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121072543</v>
+        <v>121072525</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>57462</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,38 +1135,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545935</v>
+        <v>545931</v>
       </c>
       <c r="R6" t="n">
-        <v>7206821</v>
+        <v>7206731</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2932,10 +2932,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121072540</v>
+        <v>121072541</v>
       </c>
       <c r="B22" t="n">
-        <v>78601</v>
+        <v>90983</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545926</v>
+        <v>545935</v>
       </c>
       <c r="R22" t="n">
-        <v>7206832</v>
+        <v>7206821</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3044,10 +3044,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121072541</v>
+        <v>121072540</v>
       </c>
       <c r="B23" t="n">
-        <v>90983</v>
+        <v>78601</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3060,21 +3060,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545935</v>
+        <v>545926</v>
       </c>
       <c r="R23" t="n">
-        <v>7206821</v>
+        <v>7206832</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 40735-2024 artfynd.xlsx
+++ b/artfynd/A 40735-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072532</v>
+        <v>121072540</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,7 +718,7 @@
         <v>545926</v>
       </c>
       <c r="R2" t="n">
-        <v>7206732</v>
+        <v>7206832</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072539</v>
+        <v>121072538</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>90723</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545930</v>
+        <v>545929</v>
       </c>
       <c r="R3" t="n">
-        <v>7206838</v>
+        <v>7206834</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121072545</v>
+        <v>121072528</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545915</v>
+        <v>545935</v>
       </c>
       <c r="R4" t="n">
-        <v>7206859</v>
+        <v>7206733</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121072543</v>
+        <v>121072522</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545935</v>
+        <v>545943</v>
       </c>
       <c r="R5" t="n">
-        <v>7206821</v>
+        <v>7206552</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121072525</v>
+        <v>121072548</v>
       </c>
       <c r="B6" t="n">
-        <v>57462</v>
+        <v>57504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,30 +1135,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545931</v>
+        <v>545861</v>
       </c>
       <c r="R6" t="n">
-        <v>7206731</v>
+        <v>7206925</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121072546</v>
+        <v>121072529</v>
       </c>
       <c r="B7" t="n">
-        <v>94484</v>
+        <v>91149</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,25 +1251,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545881</v>
+        <v>545921</v>
       </c>
       <c r="R7" t="n">
-        <v>7206905</v>
+        <v>7206726</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121072530</v>
+        <v>121072542</v>
       </c>
       <c r="B8" t="n">
-        <v>90983</v>
+        <v>90709</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545921</v>
+        <v>545935</v>
       </c>
       <c r="R8" t="n">
-        <v>7206728</v>
+        <v>7206821</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072534</v>
+        <v>121072531</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>88031</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,21 +1479,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545926</v>
+        <v>545922</v>
       </c>
       <c r="R9" t="n">
-        <v>7206745</v>
+        <v>7206730</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121072536</v>
+        <v>121072520</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,43 +1591,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545912</v>
+        <v>545961</v>
       </c>
       <c r="R10" t="n">
-        <v>7206852</v>
+        <v>7206539</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1659,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121072523</v>
+        <v>121072537</v>
       </c>
       <c r="B11" t="n">
-        <v>79711</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,25 +1699,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1736,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545932</v>
+        <v>545912</v>
       </c>
       <c r="R11" t="n">
-        <v>7206629</v>
+        <v>7206852</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1771,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072524</v>
+        <v>121072544</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>79714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,25 +1811,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1848,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545934</v>
+        <v>545917</v>
       </c>
       <c r="R12" t="n">
-        <v>7206628</v>
+        <v>7206851</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1883,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121072526</v>
+        <v>121072533</v>
       </c>
       <c r="B13" t="n">
-        <v>94484</v>
+        <v>78604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,25 +1923,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1960,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545931</v>
+        <v>545921</v>
       </c>
       <c r="R13" t="n">
-        <v>7206732</v>
+        <v>7206728</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1995,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121072521</v>
+        <v>121072545</v>
       </c>
       <c r="B14" t="n">
-        <v>97035</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,25 +2035,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2072,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545947</v>
+        <v>545915</v>
       </c>
       <c r="R14" t="n">
-        <v>7206549</v>
+        <v>7206859</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2107,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121072548</v>
+        <v>121072519</v>
       </c>
       <c r="B15" t="n">
-        <v>57504</v>
+        <v>90705</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,38 +2151,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545861</v>
+        <v>545961</v>
       </c>
       <c r="R15" t="n">
-        <v>7206925</v>
+        <v>7206532</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2223,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2233,7 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121072531</v>
+        <v>121072524</v>
       </c>
       <c r="B16" t="n">
-        <v>88024</v>
+        <v>78604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2276,21 +2263,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2300,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545922</v>
+        <v>545934</v>
       </c>
       <c r="R16" t="n">
-        <v>7206730</v>
+        <v>7206628</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2335,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2345,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2372,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121072519</v>
+        <v>121072547</v>
       </c>
       <c r="B17" t="n">
-        <v>90693</v>
+        <v>78604</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,21 +2375,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2412,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545961</v>
+        <v>545876</v>
       </c>
       <c r="R17" t="n">
-        <v>7206532</v>
+        <v>7206904</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2447,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2457,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121072520</v>
+        <v>121072523</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>79714</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,25 +2483,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2524,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545961</v>
+        <v>545932</v>
       </c>
       <c r="R18" t="n">
-        <v>7206539</v>
+        <v>7206629</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2559,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2569,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2596,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121072542</v>
+        <v>121072525</v>
       </c>
       <c r="B19" t="n">
-        <v>90697</v>
+        <v>57462</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2608,38 +2595,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545935</v>
+        <v>545931</v>
       </c>
       <c r="R19" t="n">
-        <v>7206821</v>
+        <v>7206731</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2671,7 +2662,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2681,7 +2672,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121072527</v>
+        <v>121072526</v>
       </c>
       <c r="B20" t="n">
-        <v>90662</v>
+        <v>94496</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,21 +2715,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2748,7 +2739,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545934</v>
+        <v>545931</v>
       </c>
       <c r="R20" t="n">
         <v>7206732</v>
@@ -2820,10 +2811,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121072538</v>
+        <v>121072543</v>
       </c>
       <c r="B21" t="n">
-        <v>90711</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2836,21 +2827,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,10 +2851,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545929</v>
+        <v>545935</v>
       </c>
       <c r="R21" t="n">
-        <v>7206834</v>
+        <v>7206821</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2895,7 +2886,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2905,7 +2896,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2932,10 +2923,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121072541</v>
+        <v>121072546</v>
       </c>
       <c r="B22" t="n">
-        <v>90983</v>
+        <v>94496</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2944,25 +2935,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2972,10 +2963,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545935</v>
+        <v>545881</v>
       </c>
       <c r="R22" t="n">
-        <v>7206821</v>
+        <v>7206905</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3007,7 +2998,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3017,7 +3008,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3044,10 +3035,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121072540</v>
+        <v>121072535</v>
       </c>
       <c r="B23" t="n">
-        <v>78601</v>
+        <v>94496</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3056,25 +3047,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3084,10 +3075,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545926</v>
+        <v>545913</v>
       </c>
       <c r="R23" t="n">
-        <v>7206832</v>
+        <v>7206851</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3119,7 +3110,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3129,7 +3120,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,10 +3147,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121072535</v>
+        <v>121072534</v>
       </c>
       <c r="B24" t="n">
-        <v>94484</v>
+        <v>78604</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3168,25 +3159,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3196,10 +3187,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545913</v>
+        <v>545926</v>
       </c>
       <c r="R24" t="n">
-        <v>7206851</v>
+        <v>7206745</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3231,7 +3222,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3241,7 +3232,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3268,10 +3259,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121072533</v>
+        <v>121072539</v>
       </c>
       <c r="B25" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3308,10 +3299,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545921</v>
+        <v>545930</v>
       </c>
       <c r="R25" t="n">
-        <v>7206728</v>
+        <v>7206838</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3343,7 +3334,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3353,7 +3344,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3380,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121072547</v>
+        <v>121072536</v>
       </c>
       <c r="B26" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3396,34 +3387,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545876</v>
+        <v>545912</v>
       </c>
       <c r="R26" t="n">
-        <v>7206904</v>
+        <v>7206852</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3492,10 +3492,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121072518</v>
+        <v>121072532</v>
       </c>
       <c r="B27" t="n">
-        <v>91052</v>
+        <v>90709</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3504,25 +3504,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545963</v>
+        <v>545926</v>
       </c>
       <c r="R27" t="n">
-        <v>7206536</v>
+        <v>7206732</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3604,10 +3604,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121072544</v>
+        <v>121072530</v>
       </c>
       <c r="B28" t="n">
-        <v>79711</v>
+        <v>90995</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3616,25 +3616,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545917</v>
+        <v>545921</v>
       </c>
       <c r="R28" t="n">
-        <v>7206851</v>
+        <v>7206728</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3716,10 +3716,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121072529</v>
+        <v>121072541</v>
       </c>
       <c r="B29" t="n">
-        <v>91137</v>
+        <v>90995</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3728,25 +3728,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545921</v>
+        <v>545935</v>
       </c>
       <c r="R29" t="n">
-        <v>7206726</v>
+        <v>7206821</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3828,10 +3828,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121072537</v>
+        <v>121072518</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>91064</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3840,25 +3840,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3868,10 +3868,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545912</v>
+        <v>545963</v>
       </c>
       <c r="R30" t="n">
-        <v>7206852</v>
+        <v>7206536</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3940,10 +3940,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121072528</v>
+        <v>121072527</v>
       </c>
       <c r="B31" t="n">
-        <v>78601</v>
+        <v>90674</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3952,25 +3952,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545935</v>
+        <v>545934</v>
       </c>
       <c r="R31" t="n">
-        <v>7206733</v>
+        <v>7206732</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121072522</v>
+        <v>121072521</v>
       </c>
       <c r="B32" t="n">
-        <v>78601</v>
+        <v>97048</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4064,25 +4064,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545943</v>
+        <v>545947</v>
       </c>
       <c r="R32" t="n">
-        <v>7206552</v>
+        <v>7206549</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
